--- a/r5-TC-FHIR-AG-Scheduling-R5-135-61---inconsistent-data-in-examples/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-135-61---inconsistent-data-in-examples/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T15:40:28+00:00</t>
+    <t>2026-02-20T12:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-135-61---inconsistent-data-in-examples/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-135-61---inconsistent-data-in-examples/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T12:10:17+00:00</t>
+    <t>2026-02-20T12:49:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
